--- a/results/04_final_refined_daily_hydroclimate_data/904/Wet_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/904/Wet_bulb_temp_06h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -441,8 +441,8 @@
       <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4">
-        <v>16</v>
+      <c r="D4" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -483,8 +483,8 @@
       <c r="C7">
         <v>6</v>
       </c>
-      <c r="D7" t="s">
-        <v>4</v>
+      <c r="D7">
+        <v>18.2</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -497,8 +497,8 @@
       <c r="C8">
         <v>7</v>
       </c>
-      <c r="D8" t="s">
-        <v>4</v>
+      <c r="D8">
+        <v>17.4</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -511,8 +511,8 @@
       <c r="C9">
         <v>8</v>
       </c>
-      <c r="D9" t="s">
-        <v>4</v>
+      <c r="D9">
+        <v>15.8</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -525,8 +525,8 @@
       <c r="C10">
         <v>9</v>
       </c>
-      <c r="D10" t="s">
-        <v>4</v>
+      <c r="D10">
+        <v>16.8</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -539,8 +539,8 @@
       <c r="C11">
         <v>10</v>
       </c>
-      <c r="D11" t="s">
-        <v>4</v>
+      <c r="D11">
+        <v>15.9</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -665,8 +665,8 @@
       <c r="C20">
         <v>19</v>
       </c>
-      <c r="D20" t="s">
-        <v>4</v>
+      <c r="D20">
+        <v>15.7</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -707,8 +707,8 @@
       <c r="C23">
         <v>22</v>
       </c>
-      <c r="D23" t="s">
-        <v>4</v>
+      <c r="D23">
+        <v>14.7</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -778,7 +778,7 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>17.4</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -805,8 +805,8 @@
       <c r="C30">
         <v>29</v>
       </c>
-      <c r="D30" t="s">
-        <v>4</v>
+      <c r="D30">
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/904/Wet_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/904/Wet_bulb_temp_06h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Year</t>
   </si>
@@ -26,9 +26,6 @@
   </si>
   <si>
     <t>Wet_bulb_temp_06h00</t>
-  </si>
-  <si>
-    <t>NaN</t>
   </si>
 </sst>
 </file>
@@ -413,8 +410,8 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
-        <v>4</v>
+      <c r="D2">
+        <v>16.8</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -427,8 +424,8 @@
       <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
-        <v>4</v>
+      <c r="D3">
+        <v>15.8</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -441,8 +438,8 @@
       <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4" t="s">
-        <v>4</v>
+      <c r="D4">
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -455,8 +452,8 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5" t="s">
-        <v>4</v>
+      <c r="D5">
+        <v>17.4</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -469,8 +466,8 @@
       <c r="C6">
         <v>5</v>
       </c>
-      <c r="D6" t="s">
-        <v>4</v>
+      <c r="D6">
+        <v>16.4</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -484,7 +481,7 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>18.2</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -568,7 +565,7 @@
         <v>12</v>
       </c>
       <c r="D13">
-        <v>17.2</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -582,7 +579,7 @@
         <v>13</v>
       </c>
       <c r="D14">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -596,7 +593,7 @@
         <v>14</v>
       </c>
       <c r="D15">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -623,8 +620,8 @@
       <c r="C17">
         <v>16</v>
       </c>
-      <c r="D17" t="s">
-        <v>4</v>
+      <c r="D17">
+        <v>15.8</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -637,8 +634,8 @@
       <c r="C18">
         <v>17</v>
       </c>
-      <c r="D18" t="s">
-        <v>4</v>
+      <c r="D18">
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -651,8 +648,8 @@
       <c r="C19">
         <v>18</v>
       </c>
-      <c r="D19" t="s">
-        <v>4</v>
+      <c r="D19">
+        <v>16.8</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -693,8 +690,8 @@
       <c r="C22">
         <v>21</v>
       </c>
-      <c r="D22" t="s">
-        <v>4</v>
+      <c r="D22">
+        <v>16.8</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -721,8 +718,8 @@
       <c r="C24">
         <v>23</v>
       </c>
-      <c r="D24" t="s">
-        <v>4</v>
+      <c r="D24">
+        <v>17.2</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -735,8 +732,8 @@
       <c r="C25">
         <v>24</v>
       </c>
-      <c r="D25" t="s">
-        <v>4</v>
+      <c r="D25">
+        <v>15.8</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -763,8 +760,8 @@
       <c r="C27">
         <v>26</v>
       </c>
-      <c r="D27" t="s">
-        <v>4</v>
+      <c r="D27">
+        <v>17.6</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -791,8 +788,8 @@
       <c r="C29">
         <v>28</v>
       </c>
-      <c r="D29" t="s">
-        <v>4</v>
+      <c r="D29">
+        <v>17.2</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -819,8 +816,8 @@
       <c r="C31">
         <v>30</v>
       </c>
-      <c r="D31" t="s">
-        <v>4</v>
+      <c r="D31">
+        <v>14.8</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -833,8 +830,8 @@
       <c r="C32">
         <v>31</v>
       </c>
-      <c r="D32" t="s">
-        <v>4</v>
+      <c r="D32">
+        <v>15.6</v>
       </c>
     </row>
   </sheetData>

--- a/results/04_final_refined_daily_hydroclimate_data/904/Wet_bulb_temp_06h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/904/Wet_bulb_temp_06h00_timeseries.xlsx
@@ -439,7 +439,7 @@
         <v>3</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -537,7 +537,7 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>15.9</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -565,7 +565,7 @@
         <v>12</v>
       </c>
       <c r="D13">
-        <v>16.5</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -579,7 +579,7 @@
         <v>13</v>
       </c>
       <c r="D14">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -593,7 +593,7 @@
         <v>14</v>
       </c>
       <c r="D15">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -635,7 +635,7 @@
         <v>17</v>
       </c>
       <c r="D18">
-        <v>16</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -663,7 +663,7 @@
         <v>19</v>
       </c>
       <c r="D20">
-        <v>15.7</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -677,7 +677,7 @@
         <v>20</v>
       </c>
       <c r="D21">
-        <v>16.8</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -705,7 +705,7 @@
         <v>22</v>
       </c>
       <c r="D23">
-        <v>14.7</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -747,7 +747,7 @@
         <v>25</v>
       </c>
       <c r="D26">
-        <v>16.5</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -775,7 +775,7 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>16.5</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -803,7 +803,7 @@
         <v>29</v>
       </c>
       <c r="D30">
-        <v>15</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="31" spans="1:4">
